--- a/deliverables/青岛抚顺路和哈尔滨路路口交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛抚顺路和哈尔滨路路口交通事故_伤情伤残与行动表_20260817.xlsx
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>胡某当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
+          <t>胡志远当时在为刘孝春家卸货搬运，驾驶/使用刘家三轮车。卸完第一趟，回装第二趟：贴护栏上坡，准备左拐去下方装货再往楼上拉。因护栏开口，须先向上借道调整，再掉头。8 月 18 日口述双方都往上走。后方黄色美团二轮碰撞，三轮侧翻，脚踏板压伤右脚。交警称视频能看清过程；家属称监控可能看不清护栏。护栏开口可以解释动作来源，但不能据此争全责。</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>对接人胡继刚；齐鲁转写 33 床胡志远；用工老板口述刘孝春（转写刘小春）；有人问过孙总被否认</t>
+          <t>齐鲁病历、腕带、出院记录均为胡志远；对接人胡继刚；老板刘孝春（转写刘小春）</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>身份证、病历首页、微信实名，对外材料只用证件姓名</t>
+          <t>身份证是否与病历同名；对外法律文书只用证件姓名</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>齐鲁手术 8/15；人已到人民医院；保险侧确认二甲可赔、比例待定</t>
+          <t>齐鲁住院号 0001519455；门诊号 0002750430；8/14 19:01 手术；8/17 08:00 出院；出院记录、三份 CT、破伤风处方已归档</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>住院号；书面赔付比例；手术记录和植入物清单（钢钉根数）</t>
+          <t>人民医院住院号；书面赔付比例；完整手术记录和植入物编码；病案室复印（出院后 10 个工作日，博施楼 1 楼）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>齐鲁医院云影像 · 谁受伤、伤了什么（2026-08-17 核对）</t>
+          <t>齐鲁医院云影像 + 出院记录 · 谁受伤、伤了什么（2026-08-19 核对病历）</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       <c r="C5" s="3" t="inlineStr">
         <is>
           <t>右踝关节CT平扫（薄层）＋骨三维成像
-住院 · 手足与显微重建外科 · 已审核</t>
+住院 · 手足与显微重建外科 · 33 床 · 已审核</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -3390,14 +3390,14 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>患者：胡** / 男 / 64岁　　医院：山东大学齐鲁医院（青岛）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>患者：胡志远 / 男 / 64岁　　门诊号 0002750430　　住院号 0001519455　　11D 手足与显微重建外科病区 33床</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>报告页注明：本报告仅供临床医生参考，不作任何证明。 这是影像诊断，不是伤残鉴定。</t>
+          <t>手术：2026-08-14 19:01 右踝关节骨折脱位切开复位内外固定、韧带缝合、软组织清创、VSD 负压吸引。出院诊断：右开放性踝关节骨折；右开放性踝关节脱位；右踝部韧带断裂；右踝挫伤并皮肤坏死。报告页注明：本报告仅供临床医生参考，不作任何证明。</t>
         </is>
       </c>
     </row>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>仅伤者本人：64 岁男性胡某（云影像脱敏为胡**）。家属胡继刚、美团骑手均无本次伤残材料。</t>
+          <t>仅伤者本人：64 岁男性胡志远（病历名；云影像脱敏为胡**）。家属胡继刚、美团骑手均无本次伤残材料。</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>与本次事故相关、日后可能构成评残基础的，是右踝骨折脱位 + 胫骨远端骨折 + 腓骨近端骨折治疗后残留的踝关节功能、行走能力、畸形或疼痛。右足退变、骨刺不计入本次。</t>
+          <t>与本次事故相关、日后可能构成评残基础的，是右开放性踝关节骨折脱位、韧带断裂、皮肤坏死清创及 VSD、胫骨远端和腓骨近端骨折治疗后残留的踝关节功能、行走能力、畸形或疼痛。高血压、糖尿病和右足退变、骨刺不计入本次。</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>保存三份 CT 报告、影像、手术记录、入院出院记录、医嘱和发票原件</t>
+          <t>保存三份 CT 报告、出院记录、腕带信息、破伤风处方；再向病案室要完整手术记录和植入物清单</t>
         </is>
       </c>
       <c r="C11" s="3" t="n"/>
@@ -3679,11 +3679,12 @@
         <is>
           <t>• 右侧胫骨远端骨折（断端移位）
 • 右侧腓骨近端骨折（断端移位）
-• 右踝关节半脱位（对位不良，胫距关节间隙增宽）
-• 右距骨内缘撕脱性骨折
-• 右外踝撕脱性骨折
+• 右踝关节半脱位（CT）；出院诊断为右开放性踝关节骨折、右开放性踝关节脱位
+• 右距骨内缘撕脱性骨折、右外踝撕脱性骨折
+• 右踝部韧带断裂（出院诊断）
+• 右踝挫伤并皮肤坏死；内踝碾挫伤创面深达骨质（入院查体）
 • 右小腿、踝关节软组织肿胀
-• 2026-08-15 已行右踝关节骨折内外固定术，复查固定在位、位线可，软组织仍肿</t>
+• 2026-08-14 19:01 行切开复位内外固定、韧带缝合、清创、VSD 负压吸引；外固定架及克氏针固定可靠</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -3701,7 +3702,8 @@
       <c r="B4" s="5" t="inlineStr">
         <is>
           <t>• 右足组成骨结构完整，诸关节在位，未见本次外伤性骨折
-• 右足退行性变、跟骨骨刺、第一跖骨头囊变：属退变/陈旧改变，一般不计入本次交通事故伤残</t>
+• 右足退行性变、跟骨骨刺、第一跖骨头囊变：属退变/陈旧改变，一般不计入本次交通事故伤残
+• 高血压、糖尿病：既往病，写在出院诊断里是为围手术期管理，不向肇事方按事故伤索赔</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -3757,7 +3759,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>术后 CT 结论是「内外固定术后，内外固定在位」，以手术记录和术后 CT 为准，不以口述根数为准。</t>
+          <t>出院记录写的是外固定架及克氏针，未写锁定钉根数。完整手术记录和植入物清单仍要向病案室要，不以口述根数为准。</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3776,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>同日住院 CT 在手足与显微重建外科，证明当时仍在齐鲁医院住院术后复查，并未结束治疗。</t>
+          <t>出院记录：2026-08-14 14:14 入院，2026-08-17 08:00 出院，住院 3 天。8 月 15 日是术后 CT，人还在齐鲁 33 床。</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3839,12 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>录音写成「胡志远」</t>
+          <t>录音写成「胡志远」、对外写胡某</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>家属对接人是儿子胡继刚。伤者写胡某。姓名以身份证、病历首页为准。</t>
+          <t>齐鲁门诊病历、腕带、出院记录姓名均为胡志远。家属口语称老爷子。法律文书以身份证和病历首页为准。</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4107,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>不要把现在当成康复期。8 月 15 日术后 CT 仍写软组织肿胀、内外固定刚做完，到 17 日只过了两天。朋友说「已经康复期就别折腾」与影像时间轴不符。</t>
+          <t>不要把现在当成康复期。手术是 8 月 14 日 19:01，出院 8 月 17 日 08:00，出院时仍带 VSD 和外固定架，医嘱继续负压吸引、根据创面二期治疗。8 月 15 日术后 CT 仍写软组织肿胀。朋友说「已经康复期就别折腾」与病历不符。</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4212,10 +4214,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>急诊右小腿CT（10008056847）</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr"/>
+          <t>破伤风人免疫球蛋白 250iu 肌注</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>270</v>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>已付待核</t>
@@ -4234,7 +4238,7 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>齐鲁医院</t>
+          <t>急诊处方，医师甄洪岩</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4250,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>急诊右足CT（10008056848）</t>
+          <t>急诊右小腿CT（10008056847）</t>
         </is>
       </c>
       <c r="C4" s="15" t="inlineStr"/>
@@ -4268,19 +4272,19 @@
       <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>齐鲁医院</t>
+          <t>齐鲁医院 13:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>住院右踝CT术后复查（10008059257）</t>
+          <t>急诊右足CT（10008056848）</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr"/>
@@ -4302,19 +4306,19 @@
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>手足与显微重建外科</t>
+          <t>齐鲁医院 13:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14 19:01</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>右踝骨折内外固定手术</t>
+          <t>右踝骨折脱位切开复位内外固定+韧带缝合+清创+VSD</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr"/>
@@ -4336,15 +4340,19 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>以手术记录为准</t>
+          <t>出院记录已载术式；植入物编码仍缺</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>住院押金/预缴</t>
+          <t>住院右踝CT术后复查（10008059257）</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr"/>
@@ -4366,7 +4374,7 @@
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>费用口径确认 4 万，须对账单</t>
+          <t>手足与显微重建外科 33 床</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4382,7 @@
       <c r="A8" s="5" t="inlineStr"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>药品（院内）</t>
+          <t>住院押金/预缴</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr"/>
@@ -4396,7 +4404,7 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>医保范围内用药，保险可赔、比例待定</t>
+          <t>费用口径确认 4 万，须对账单</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4412,7 @@
       <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>护工费</t>
+          <t>药品（院内）</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr"/>
@@ -4426,7 +4434,7 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>24小时一对一，合同+发票；按责比例报</t>
+          <t>医保范围内用药，保险可赔、比例待定</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4442,7 @@
       <c r="A10" s="5" t="inlineStr"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>护理耗材（垫、便盆等）</t>
+          <t>护工费</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr"/>
@@ -4454,73 +4462,71 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>24小时一对一，合同+发票；按责比例报</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>护理耗材（垫、便盆等）</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>已付待核</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>家属</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>待贴</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>转院救护车</t>
         </is>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C12" s="15" t="n">
         <v>160</v>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>已付待核</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>家属</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>待贴</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>预估150，实收160，必须发票</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr"/>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>用工方垫付现金</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>已付待写收据</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>乔刘记商贸/刘孝春</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>收据</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>写明垫付不是借款、不是了结、不冲抵欠薪</t>
+          <t>预估150，实收160，必须发票</t>
         </is>
       </c>
     </row>
@@ -4528,31 +4534,31 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>未结工钱</t>
+          <t>用工方垫付现金</t>
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>未付</t>
+          <t>已付待写收据</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>刘孝春</t>
+          <t>乔刘记商贸/刘孝春</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>欠条</t>
+          <t>收据</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>另写一张，不乘 30%，不和 3 万垫付混</t>
+          <t>写明垫付不是借款、不是了结、不冲抵欠薪</t>
         </is>
       </c>
     </row>
@@ -4560,42 +4566,74 @@
       <c r="A14" s="5" t="inlineStr"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>责任方已付（美团侧）</t>
+          <t>未结工钱</t>
         </is>
       </c>
       <c r="C14" s="15" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>待拉群</t>
+          <t>未付</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>骑手/平台险</t>
+          <t>刘孝春</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>欠条</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
+          <t>另写一张，不乘 30%，不和 3 万垫付混</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>责任方已付（美团侧）</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>待拉群</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>骑手/平台险</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>保单和限额待骑手拉群</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>合计（仅填写了数字的行）</t>
         </is>
       </c>
-      <c r="C16" s="16">
-        <f>SUM(C3:C14)</f>
+      <c r="C17" s="16">
+        <f>SUM(C3:C15)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/青岛抚顺路和哈尔滨路路口交通事故_伤情伤残与行动表_20260817.xlsx
+++ b/deliverables/青岛抚顺路和哈尔滨路路口交通事故_伤情伤残与行动表_20260817.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>用发票做台账，分清：刘孝春垫付现金 3 万是一笔；费用口径 4 万是累计还是另一笔。逐项贴票：齐鲁手术/CT、人民医院、药品、护工合同+发票（本院合作一对一 24 小时）、救护车 160 元。医保已报金额单独记，避免重复报。记录 13 的 8000 元、蒋玉年不是本案。无票现金先不要对外报。</t>
+          <t>用发票做台账，分清：刘孝春垫付现金 3 万是一笔；费用口径 4 万是累计还是另一笔。逐项贴票：齐鲁手术/CT、人民医院、药品、护工（医院推荐一对一 24 小时，300 元/天，须合同+发票）、救护车 160 元。医保已报金额单独记，避免重复报。记录 13 的 8000 元、蒋玉年不是本案。无票现金先不要对外报。</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -907,12 +907,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>处理交通事故的本地律师（岳父场外即可）；家属不拍板</t>
+          <t>岳父场外把关；家属不拍板</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>律师看监控复制件或到场查看、看内部牌和灯坏情况后，书面或微信明确「走简易」或「走一般」。同意任何责任比例之前必须看完。现在不请诉讼律师当面谈、不先发律师函。</t>
+          <t>岳父看监控复制件或指导查看、看内部牌和灯坏情况后，书面或微信明确「走简易」或「走一般」。同意任何责任比例之前必须看完。现在不到场见骑手或刘孝春、不先发律师函。</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>医院合作一对一 24 小时合同+发票；出院后仍不能自理的，按医嘱天数和当地护工价。青岛约 300–350 元/天。</t>
+          <t>医院推荐一对一 24 小时已请，日单价 300 元。必须书面合同、发票、护理记录、开始日期。出院后仍不能自理的，按医嘱天数续。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2279,17 +2279,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>现在按不能自理、应请 24 小时一对一</t>
+          <t>医院推荐一对一 24 小时已请，日单价 300 元（2026-08-22 确认）</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>合同、发票、护理记录、日单价、开始日期</t>
+          <t>书面合同（写明一对一、公司名、开始日期、300 元/天）、发票抬头、护理记录；刘若垫付另开收据</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>护士站本院合作公司</t>
+          <t>护工公司 + 家属</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>在同意任何责任比例或程序选择前，让处理交通事故的本地律师查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
+          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。不到场见骑手，不先发函。</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>本地交通事故律师（岳父场外）。驾驶人有证，无证风险下降；无青岛市号牌风险仍在。家属不自己拍板。现在不请诉讼律师当面谈。</t>
+          <t>岳父（执业三十余年，场外把关）。驾驶人有证，无证风险下降；无青岛市号牌风险仍在。家属不自己拍板。现在不请诉讼律师当面谈。</t>
         </is>
       </c>
     </row>
@@ -4736,12 +4736,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>本地交通事故律师（岳父场外）</t>
+          <t>岳父（执业三十余年，场外把关）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>在同意任何责任比例或程序选择前，让处理交通事故的本地律师查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。</t>
+          <t>在同意任何责任比例或程序选择前，查看监控和车辆材料，尤其评估一般程序可能带来的车辆与驾驶资格风险。不到场见骑手，不先发函。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
